--- a/questionnaire_templates/018_student_stress_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/018_student_stress_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Stress Level</t>
+          <t>How would you rate your current stress level?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anxiety And Worrying</t>
+          <t>How often do you experience anxiety or worrying thoughts?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Physical Discomfort</t>
+          <t>How would you rate your physical discomfort level?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Difficulty Sleeping</t>
+          <t>How often do you experience difficulty sleeping?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lack Of Pleasure</t>
+          <t>What activities give you a sense of pleasure and relaxation?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anger Irritability</t>
+          <t>How often do you experience anger or irritability?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Social Withdrawal</t>
+          <t>How often do you feel socially withdrawn?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Academic Burden</t>
+          <t>How would you rate your current academic burden?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lack Of Interest</t>
+          <t>What activities interest you?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fear And Panic</t>
+          <t>How often do you experience fear or panic?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lack Of Energy</t>
+          <t>How would you rate your current energy level?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,312 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Difficulty Concentrating</t>
+          <t>How often do you experience difficulty concentrating?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>lack_of_pleasure</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Lack Of Pleasure</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>feeling_sad_or_depressed</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Feeling Sad Or Depressed</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>lack_of_pleasure</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lack Of Pleasure</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>general_stress_level</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>General Stress Level</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>anxiety_and_worrying</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Anxiety And Worrying</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>academic_burden</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Academic Burden</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>difficulty_sleeping</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Difficulty Sleeping</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>lack_of_interest</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lack Of Interest</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fear_and_panic</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fear And Panic</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>lack_of_energy</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lack Of Energy</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>difficulty_concentrating</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Difficulty Concentrating</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>lack_of_pleasure</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Lack Of Pleasure</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>feeling_sad_or_depressed</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Feeling Sad Or Depressed</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,7 +802,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,51 +827,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>feeling_sad_or_depressed_choices</t>
+          <t>lack_of_pleasure_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Physical activity</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>feeling_sad_or_depressed_choices</t>
+          <t>lack_of_pleasure_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>hobbies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Hobbies</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feeling_sad_or_depressed_choices</t>
+          <t>lack_of_pleasure_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>socializing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Socializing</t>
         </is>
       </c>
     </row>
@@ -1182,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>physical_activity</t>
+          <t>relaxation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Physical activity</t>
+          <t>Relaxation</t>
         </is>
       </c>
     </row>
@@ -1199,97 +900,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hobbies</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hobbies</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lack_of_pleasure_choices</t>
+          <t>lack_of_interest_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>socializing</t>
+          <t>physical_activity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Socializing</t>
+          <t>Physical activity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lack_of_pleasure_choices</t>
+          <t>lack_of_interest_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>relaxation</t>
+          <t>hobbies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Relaxation</t>
+          <t>Hobbies</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lack_of_pleasure_choices</t>
+          <t>lack_of_interest_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exercise</t>
+          <t>socializing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Socializing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>general_stress_level_choices</t>
+          <t>lack_of_interest_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>relaxation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Relaxation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>general_stress_level_choices</t>
+          <t>lack_of_interest_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Exercise</t>
         </is>
       </c>
     </row>
